--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -32040,7 +32040,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -34089,7 +34089,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -35397,7 +35397,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -35737,7 +35737,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -36462,17 +36462,17 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">

--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N510"/>
+  <dimension ref="A1:N512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30029605;2025,AP,SAIC-VW,ITC-Slash automation, 250230, M,Equipment</t>
+          <t>30029605-2025,AP,SAIC-VW,ITC-Slash automation, 250230, M,Equipment</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>30027253;2025,AP,Geely,HS11-light,welding,250061,M,Equipment</t>
+          <t>30027253-2025,AP,Geely,HS11-light,welding,250061,M,Equipment</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>30025636;2025,AP,Brilliance-BMW,Ncar-lght,assemble,240292,T,Equipment</t>
+          <t>30025636-2025,AP,Brilliance-BMW,Ncar-lght,assemble,240292,T,Equipment</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>30022667;2025,AP,SERES Motors,F3-CNSL,Lamination,240178,M,Equipment</t>
+          <t>30022667-2025,AP,SERES Motors,F3-CNSL,Lamination,240178,M,Equipment</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -32097,7 +32097,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -32256,7 +32256,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -33809,7 +33809,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -33881,22 +33881,22 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -34132,7 +34132,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N469" t="inlineStr"/>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>0.9394</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -34577,7 +34581,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -34721,7 +34725,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -34789,7 +34793,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -35397,7 +35401,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -36061,7 +36065,7 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -36125,7 +36129,7 @@
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -36189,7 +36193,7 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -36253,7 +36257,7 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -36901,6 +36905,142 @@
         </is>
       </c>
       <c r="N510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>30035162</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>30035162-2026,AP,BJEV,X90,Lamination,260133,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>30035162</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>260133</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>BJEVX90Lamination</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>30035161</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>30035161-2026,AP,BJEV,X90,Lamination,260132,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>30035161</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>260132</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>BJEVX90Lamination</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N512"/>
+  <dimension ref="A1:N513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30030470;2026,AP,BMW,G60 Armrest,Lamination,250292,M,Equipment</t>
+          <t>30030470-2026,AP,BMW,G60 Armrest,Lamination,250292,M,Equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30030326;2025,AP,XPENG,JH-A-mirror,assy,250270,XT,Equipment</t>
+          <t>30030326-2025,AP,XPENG,JH-A-mirror,assy,250270,XT,Equipment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30030147;2026,AP,SERES Motors,F1L-Sunvisior wrap,250251,T,Equipment</t>
+          <t>30030147-2026,AP,SERES Motors,F1L-Sunvisior wrap,250251,T,Equipment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30029653;2025,AP,SERES Motors,F1L-Sun visor,Assy,250232,T,Equipment</t>
+          <t>30029653-2025,AP,SERES Motors,F1L-Sun visor,Assy,250232,T,Equipment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30029639;2025,AP,Brilliance-BMW,Ncar-light,assemble,250227,XT,Equipment</t>
+          <t>30029639-2025,AP,Brilliance-BMW,Ncar-light,assemble,250227,XT,Equipment</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30028591;2026,AP,Li Auto,LAMINATION,250182,T,Equipment</t>
+          <t>30028591-2026,AP,Li Auto,LAMINATION,250182,T,Equipment</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30028576;2026,AP,Li Auto,W04,Lamination,250179,M,Equipment</t>
+          <t>30028576-2026,AP,Li Auto,W04,Lamination,250179,M,Equipment</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30028374;2025,AP,Tes,E41-U-Panel,Lamination,250154,T,Equipment</t>
+          <t>30028374-2025,AP,Tes,E41-U-Panel,Lamination,250154,T,Equipment</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>30027586;2025,AP,BYD,SA3-DP,lamination,250081,1M,Equipment</t>
+          <t>30027586-2025,AP,BYD,SA3-DP,lamination,250081,1M,Equipment</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>30027585;2025,AP,BYD,SA3-DP, Lamination, 250080,1M,Equipment</t>
+          <t>30027585-2025,AP,BYD,SA3-DP, Lamination, 250080,1M,Equipment</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>30024378;2025,AP,General Motors,L234-FC,lamination,240260,T,Equipment</t>
+          <t>30024378-2025,AP,General Motors,L234-FC,lamination,240260,T,Equipment</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>30024111;2026,AP,Mercedes-Benz,V540-IP,Lami,240240,1M,Equipment</t>
+          <t>30024111-2026,AP,Mercedes-Benz,V540-IP,Lami,240240,1M,Equipment</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>30023952;2025,NA,General Motors,L234-IP RHD,punch,240224,T,Equipment</t>
+          <t>30023952-2025,NA,General Motors,L234-IP RHD,punch,240224,T,Equipment</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>30023951;2025,NA,General Motors,L234-IP RHD,bonding,240233,T,Equipment</t>
+          <t>30023951-2025,NA,General Motors,L234-IP RHD,bonding,240233,T,Equipment</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>30023950;2025,NA,General Motors,L234-IP RHD,bonding,240232,T,Equipment</t>
+          <t>30023950-2025,NA,General Motors,L234-IP RHD,bonding,240232,T,Equipment</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>30023947;2025,NA,General Motors,L234-IP RHD,welding,240225,T,Equipment</t>
+          <t>30023947-2025,NA,General Motors,L234-IP RHD,welding,240225,T,Equipment</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>30023946;2025,NA,General Motors,L234-IP RHD,lamination,240227,T,Equipment</t>
+          <t>30023946-2025,NA,General Motors,L234-IP RHD,lamination,240227,T,Equipment</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>30022299;2025,AP,Volkswagen,VW426-DP,lam&amp;wrap,240151,1T,Equipment</t>
+          <t>30022299-2025,AP,Volkswagen,VW426-DP,lam&amp;wrap,240151,1T,Equipment</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>30022298;2025,AP,Volkswagen,VW426-DP,lam&amp;wrap,240150,1T,Equipment</t>
+          <t>30022298-2025,AP,Volkswagen,VW426-DP,lam&amp;wrap,240150,1T,Equipment</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>30020975;2026,AP,VW Group,VW426-DP, welding, 240071, 2M,Equipment</t>
+          <t>30020975-2026,AP,VW Group,VW426-DP, welding, 240071, 2M,Equipment</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -18867,7 +18867,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -31218,7 +31218,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>30031061;2025,AP,Daimler,V530-IP,EOAT,250318,2T,Equipment</t>
+          <t>30031061-2025,AP,Daimler,V530-IP,EOAT,250318,2T,Equipment</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -31233,7 +31233,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -31449,7 +31449,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Phase0</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -31521,7 +31521,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -31809,7 +31809,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -32097,7 +32097,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -32385,7 +32385,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -33601,12 +33601,12 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -33737,22 +33737,22 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -34021,7 +34021,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -34089,7 +34089,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -34301,7 +34301,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -34513,7 +34513,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -35330,7 +35330,11 @@
           <t>Chen Jiarong_陈佳荣(uchej731)</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
@@ -35401,7 +35405,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
@@ -35537,7 +35541,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -35605,7 +35609,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -35673,7 +35677,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -35741,7 +35745,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
@@ -35814,17 +35818,17 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -35873,22 +35877,22 @@
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -35937,7 +35941,7 @@
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -36001,7 +36005,7 @@
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -36257,7 +36261,7 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -36590,7 +36594,11 @@
           <t>Chen Jiarong_陈佳荣(uchej731)</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
@@ -37041,6 +37049,58 @@
         </is>
       </c>
       <c r="N512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>30035707</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>30035707-2026,AP,Brilliance-BMW,RGB 8PIN-light,assemble,260156,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>30035707</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>260156</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Brilliance-BMWRGB 8PIN-lightassemble</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N514"/>
+  <dimension ref="A1:N519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>30030389;2026,AP,SERES Motors,F2N sunvisor,Assy，250278，M,Equipment</t>
+          <t>30030389-2026,AP,SERES Motors,F2N sunvisor,Assy，250278，M,Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>30017228;2025,AP,Daimler,BR223-DP,Pre-fixing,230170,T,Equipment</t>
+          <t>30017228-2025,AP,Daimler,BR223-DP,Pre-fixing,230170,T,Equipment</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>30017227;2025,AP,Daimler,BR223-DP,Pre-fixing,230169,M,Equipment</t>
+          <t>30017227-2025,AP,Daimler,BR223-DP,Pre-fixing,230169,M,Equipment</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -25123,7 +25123,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>30016953;2025,AP,Daimler,BR223-DP,Lamination,230180,T,Equipment</t>
+          <t>30016953-2025,AP,Daimler,BR223-DP,Lamination,230180,T,Equipment</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -29295,7 +29295,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -31536,7 +31536,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -34933,17 +34933,17 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -34996,27 +34996,27 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Zhang Shuai27_张帅(uzhas1129)</t>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -36685,7 +36685,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -36821,7 +36821,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -37082,7 +37082,11 @@
           <t>Chen Jiarong_陈佳荣(uchej731)</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>Phase 1 Quotation</t>
@@ -37090,17 +37094,17 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -37197,6 +37201,342 @@
         </is>
       </c>
       <c r="N514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>260077</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>30036184</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>30036184-2026,AP,JAC-VW,JHB-sunvisor,assem, 260180, 2T,Equipment</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>30036184</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>260180</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>JAC-VWJHB-sunvisorassem</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>30036085</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>30036085-2026,AP,SERES Motors,L97-light，assemble,260173,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Huang Sheng02_黄圣(uhuas068)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>30036085</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>260173</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>SERES MotorsL97-light，assemble260173</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>30036039</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>30036039-2026,AP,SERES Motors,L97-DAB, Lamination, 260171, 1T,Equipment</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Huang Dongfang01_黄东方(uhuad056)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>30036039</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>260171</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>SERES MotorsL97-DAB Lamination</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>30033911</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>30033911</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>260060</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>StellantisWL-DPlaminnation</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Phase0</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30028582;2026,AP,SAIC-VW,VW416-9,EOL,250177,M,Equipment</t>
+          <t>30028582-2026,AP,SAIC-VW,VW416-9,EOL,250177,M,Equipment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30028578;2026,AP,Li Auto,W04,Lamination,250181,T,Equipment</t>
+          <t>30028578-2026,AP,Li Auto,W04,Lamination,250181,T,Equipment</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30028292;2025,AP,Geely,X2411,Lamination,250147,M,Equipment</t>
+          <t>30028292-2025,AP,Geely,X2411,Lamination,250147,M,Equipment</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Post Launch</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30027581;2025,AP,Others,other,Granulator,250089,M,Equipment</t>
+          <t>30027581-2025,AP,Others,other,Granulator,250089,M,Equipment</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>30025716;2026,AP,M Auto,MX11,Fixing,250013,T,Equipment</t>
+          <t>30025716-2026,AP,M Auto,MX11,Fixing,250013,T,Equipment</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>30025715;2026,AP,M Auto,MX11,Fixing,250012,M,Equipment</t>
+          <t>30025715-2026,AP,M Auto,MX11,Fixing,250012,M,Equipment</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>30025515;2025,AP,Geely-Volvo,v44x,torque fixture,250001,T,Equipment</t>
+          <t>30025515-2025,AP,Geely-Volvo,v44x,torque fixture,250001,T,Equipment</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>30024136;2026,AP,Mercedes-Benz,V540-IP,Lami,240241,T,Equipment</t>
+          <t>30024136-2026,AP,Mercedes-Benz,V540-IP,Lami,240241,T,Equipment</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>30023368;2026,AP,Mercedes-Benz,V540-DP,Lami,240183,1M,Equipment</t>
+          <t>30023368-2026,AP,Mercedes-Benz,V540-DP,Lami,240183,1M,Equipment</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15483,7 +15483,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Post Launch</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>30020950;2024,AP,BMW,G60-Armrest,lamination,240070,T,Equipment</t>
+          <t>30020950-2024,AP,BMW,G60-Armrest,lamination,240070,T,Equipment</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>30020949;2024,AP,BMW,G60-Armrest,lamination.240069,T,Equipment</t>
+          <t>30020949-2024,AP,BMW,G60-Armrest,lamination.240069,T,Equipment</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -28632,7 +28632,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>30017004;2024,AP,VW Group,E4-FC,Welding,230083,T,Equipment</t>
+          <t>30017004-2024,AP,VW Group,E4-FC,Welding,230083,T,Equipment</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -28647,7 +28647,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -28704,7 +28704,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>30017003;2024,AP,VW Group,E4-FC,Welding.230082,M,Equipment</t>
+          <t>30017003-2024,AP,VW Group,E4-FC,Welding.230082,M,Equipment</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -28719,7 +28719,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -28776,7 +28776,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>30017002;2024,AP,VW Group,E4-DP,Pre-fixing,230128,T,Equipment</t>
+          <t>30017002-2024,AP,VW Group,E4-DP,Pre-fixing,230128,T,Equipment</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -28848,7 +28848,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>30017001;2024,AP,VW Group,E4-DP,Pre-fixing,230128,M,Equipment</t>
+          <t>30017001-2024,AP,VW Group,E4-DP,Pre-fixing,230128,M,Equipment</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -28863,7 +28863,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>30013145;2023,AP,VW Group,E4-DP,Gluing,230017,T,Equipment</t>
+          <t>30013145-2023,AP,VW Group,E4-DP,Gluing,230017,T,Equipment</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -30729,7 +30729,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -30786,7 +30786,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>30013144;2023,AP,VW Group,E4-DP,Gluing,230016,M,Equipment</t>
+          <t>30013144-2023,AP,VW Group,E4-DP,Gluing,230016,M,Equipment</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -30801,7 +30801,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -31809,7 +31809,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+          <t>Li Yanchen_李彦辰(ulixy466)</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Phase0</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -33673,7 +33673,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -34025,7 +34025,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -34532,7 +34532,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -35001,7 +35001,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -35893,7 +35893,7 @@
       <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
@@ -35957,7 +35957,7 @@
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -36021,7 +36021,7 @@
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -36085,7 +36085,7 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -36149,7 +36149,7 @@
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -36213,7 +36213,7 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -36277,7 +36277,7 @@
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -36345,7 +36345,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
@@ -36481,7 +36481,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -36549,7 +36549,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -36885,7 +36885,7 @@
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -36953,7 +36953,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -37289,7 +37289,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">

--- a/yanfeng/项目信息表/项目信息表.xlsx
+++ b/yanfeng/项目信息表/项目信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N519"/>
+  <dimension ref="A1:N521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Post Launch</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase0</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -34729,7 +34729,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -34860,22 +34860,22 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Chen Ziyi01_陈子翌(uchez443)</t>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -35069,22 +35069,22 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -35137,7 +35137,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -35316,7 +35316,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N486" t="inlineStr"/>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>0.9231</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -35341,7 +35345,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
@@ -35549,7 +35553,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -35617,7 +35621,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -35685,7 +35689,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Phase 3 Design Feasibility</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
@@ -35890,7 +35894,11 @@
           <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Feng Quanhua_冯全华(ufenq022)</t>
+        </is>
+      </c>
       <c r="E495" t="inlineStr">
         <is>
           <t>Phase 4 Manufacturing Development</t>
@@ -36617,7 +36625,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -36885,7 +36893,7 @@
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -36953,7 +36961,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -37089,7 +37097,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -37289,7 +37297,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Phase 2 Concept Definition</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -37425,7 +37433,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -37493,7 +37501,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Phase 1 Quotation</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -37537,6 +37545,142 @@
         </is>
       </c>
       <c r="N519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>30034479B/C/D</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>30034479</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>260085</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Toyota,780B,Spraying</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>30034473_</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260082,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Phase 5 Production Delivery</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>30034473</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>260082</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>SERES Motors,F2N-light</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
